--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I593"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20005,6 +20005,39 @@
         <v>379.75</v>
       </c>
       <c r="I593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="C594" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="D594" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="E594" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="F594" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="G594" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="H594" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="I594" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20021,7 +20054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26184,6 +26217,16 @@
       </c>
       <c r="B616" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -26352,28 +26395,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2297705870766351</v>
+        <v>-0.2337036405615945</v>
       </c>
       <c r="J2" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0258636186999216</v>
+        <v>0.02677192915785287</v>
       </c>
       <c r="M2" t="n">
-        <v>8.408417757633265</v>
+        <v>8.414856130842226</v>
       </c>
       <c r="N2" t="n">
-        <v>101.0090980790123</v>
+        <v>101.0539618676162</v>
       </c>
       <c r="O2" t="n">
-        <v>10.05032825727659</v>
+        <v>10.05255996588014</v>
       </c>
       <c r="P2" t="n">
-        <v>344.7867956388686</v>
+        <v>344.8297550724482</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26434,28 +26477,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1377635935758973</v>
+        <v>-0.1395510321307185</v>
       </c>
       <c r="J3" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K3" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1323864476152099</v>
+        <v>0.1349722930680487</v>
       </c>
       <c r="M3" t="n">
-        <v>2.082435589260377</v>
+        <v>2.085920206896726</v>
       </c>
       <c r="N3" t="n">
-        <v>6.390680480350616</v>
+        <v>6.425213088415915</v>
       </c>
       <c r="O3" t="n">
-        <v>2.527979525302888</v>
+        <v>2.534800404058654</v>
       </c>
       <c r="P3" t="n">
-        <v>351.2689307175093</v>
+        <v>351.2883065871462</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26516,28 +26559,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1244791063501915</v>
+        <v>-0.1252597395235887</v>
       </c>
       <c r="J4" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K4" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1119643725619108</v>
+        <v>0.1134400291477657</v>
       </c>
       <c r="M4" t="n">
-        <v>1.998382733681881</v>
+        <v>1.999374131731945</v>
       </c>
       <c r="N4" t="n">
-        <v>6.314498185351936</v>
+        <v>6.312491919880454</v>
       </c>
       <c r="O4" t="n">
-        <v>2.512866527564076</v>
+        <v>2.512467297275818</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4735789357867</v>
+        <v>352.4820410149788</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26598,28 +26641,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1073245992238059</v>
+        <v>-0.1088709431721643</v>
       </c>
       <c r="J5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L5" t="n">
-        <v>0.107200896900505</v>
+        <v>0.109652951331636</v>
       </c>
       <c r="M5" t="n">
-        <v>1.721234265375935</v>
+        <v>1.724594682956007</v>
       </c>
       <c r="N5" t="n">
-        <v>4.928891490638247</v>
+        <v>4.95449057274376</v>
       </c>
       <c r="O5" t="n">
-        <v>2.220110693330008</v>
+        <v>2.225868498529003</v>
       </c>
       <c r="P5" t="n">
-        <v>351.015191108369</v>
+        <v>351.0319535076561</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26680,28 +26723,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02769258040979229</v>
+        <v>-0.02826119707463175</v>
       </c>
       <c r="J6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008508762020472127</v>
+        <v>0.008881711363330602</v>
       </c>
       <c r="M6" t="n">
-        <v>1.681978068686365</v>
+        <v>1.681876458312768</v>
       </c>
       <c r="N6" t="n">
-        <v>4.591395819084299</v>
+        <v>4.588238442430874</v>
       </c>
       <c r="O6" t="n">
-        <v>2.142754260078439</v>
+        <v>2.142017376780794</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2900625304101</v>
+        <v>355.2962263464146</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26762,28 +26805,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1486485968702569</v>
+        <v>-0.1489167582274572</v>
       </c>
       <c r="J7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L7" t="n">
-        <v>0.140841294408977</v>
+        <v>0.1417002756191235</v>
       </c>
       <c r="M7" t="n">
-        <v>2.078207700336674</v>
+        <v>2.076162291912568</v>
       </c>
       <c r="N7" t="n">
-        <v>6.925647698627226</v>
+        <v>6.91498850717897</v>
       </c>
       <c r="O7" t="n">
-        <v>2.631662535095871</v>
+        <v>2.629636573212916</v>
       </c>
       <c r="P7" t="n">
-        <v>373.4017149613954</v>
+        <v>373.4046218358638</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -26844,28 +26887,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1201600383375863</v>
+        <v>-0.1216505028167031</v>
       </c>
       <c r="J8" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K8" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04851964548457632</v>
+        <v>0.04973942771155082</v>
       </c>
       <c r="M8" t="n">
-        <v>3.023406777202164</v>
+        <v>3.02508400670277</v>
       </c>
       <c r="N8" t="n">
-        <v>14.54781277787161</v>
+        <v>14.55478452355426</v>
       </c>
       <c r="O8" t="n">
-        <v>3.814159511330328</v>
+        <v>3.81507333134689</v>
       </c>
       <c r="P8" t="n">
-        <v>385.9831550057792</v>
+        <v>385.9993116705036</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -26907,7 +26950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I593"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54773,6 +54816,53 @@
         </is>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-36.63914889259338,174.7507732278765</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-36.63961586132606,174.75006766142394</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-36.640031577375524,174.7493148126445</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-36.64047074747929,174.74858985495652</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-36.64101358007339,174.74798869812918</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>-36.64157066815017,174.74741315600298</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>-36.64214886767008,174.74689113985855</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20038,6 +20038,72 @@
         <v>378.5</v>
       </c>
       <c r="I594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>330.36</v>
+      </c>
+      <c r="C595" t="n">
+        <v>342.31</v>
+      </c>
+      <c r="D595" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="E595" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="F595" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="G595" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="H595" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="C596" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="D596" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="E596" t="n">
+        <v>344</v>
+      </c>
+      <c r="F596" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="G596" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="H596" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="I596" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20054,7 +20120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26227,6 +26293,26 @@
       </c>
       <c r="B617" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
@@ -26395,28 +26481,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2337036405615945</v>
+        <v>-0.2387861357712159</v>
       </c>
       <c r="J2" t="n">
+        <v>595</v>
+      </c>
+      <c r="K2" t="n">
         <v>593</v>
       </c>
-      <c r="K2" t="n">
-        <v>591</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02677192915785287</v>
+        <v>0.02806419831520612</v>
       </c>
       <c r="M2" t="n">
-        <v>8.414856130842226</v>
+        <v>8.413240344364191</v>
       </c>
       <c r="N2" t="n">
-        <v>101.0539618676162</v>
+        <v>100.8972238466646</v>
       </c>
       <c r="O2" t="n">
-        <v>10.05255996588014</v>
+        <v>10.04476101491044</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8297550724482</v>
+        <v>344.8853692000234</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26477,28 +26563,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1395510321307185</v>
+        <v>-0.1429880415905856</v>
       </c>
       <c r="J3" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K3" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1349722930680487</v>
+        <v>0.1400475730807114</v>
       </c>
       <c r="M3" t="n">
-        <v>2.085920206896726</v>
+        <v>2.092312605052551</v>
       </c>
       <c r="N3" t="n">
-        <v>6.425213088415915</v>
+        <v>6.488013378349788</v>
       </c>
       <c r="O3" t="n">
-        <v>2.534800404058654</v>
+        <v>2.547157902123421</v>
       </c>
       <c r="P3" t="n">
-        <v>351.2883065871462</v>
+        <v>351.3256315615312</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26559,28 +26645,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1252597395235887</v>
+        <v>-0.1266417022312566</v>
       </c>
       <c r="J4" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K4" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1134400291477657</v>
+        <v>0.1161847262111008</v>
       </c>
       <c r="M4" t="n">
-        <v>1.999374131731945</v>
+        <v>2.000363437281443</v>
       </c>
       <c r="N4" t="n">
-        <v>6.312491919880454</v>
+        <v>6.304917439315467</v>
       </c>
       <c r="O4" t="n">
-        <v>2.512467297275818</v>
+        <v>2.510959465884598</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4820410149788</v>
+        <v>352.4970487490464</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26641,28 +26727,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1088709431721643</v>
+        <v>-0.1118485717080466</v>
       </c>
       <c r="J5" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K5" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.109652951331636</v>
+        <v>0.1144746302792888</v>
       </c>
       <c r="M5" t="n">
-        <v>1.724594682956007</v>
+        <v>1.731080743029618</v>
       </c>
       <c r="N5" t="n">
-        <v>4.95449057274376</v>
+        <v>5.001106523466578</v>
       </c>
       <c r="O5" t="n">
-        <v>2.225868498529003</v>
+        <v>2.236315389981158</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0319535076561</v>
+        <v>351.0642897547812</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26723,28 +26809,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02826119707463175</v>
+        <v>-0.02919530724700642</v>
       </c>
       <c r="J6" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K6" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008881711363330602</v>
+        <v>0.009527991472864206</v>
       </c>
       <c r="M6" t="n">
-        <v>1.681876458312768</v>
+        <v>1.680706257534211</v>
       </c>
       <c r="N6" t="n">
-        <v>4.588238442430874</v>
+        <v>4.579102957731908</v>
       </c>
       <c r="O6" t="n">
-        <v>2.142017376780794</v>
+        <v>2.139883865477729</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2962263464146</v>
+        <v>355.3063704939107</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26805,28 +26891,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1489167582274572</v>
+        <v>-0.1489005613711218</v>
       </c>
       <c r="J7" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K7" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1417002756191235</v>
+        <v>0.142546162410966</v>
       </c>
       <c r="M7" t="n">
-        <v>2.076162291912568</v>
+        <v>2.070482279671596</v>
       </c>
       <c r="N7" t="n">
-        <v>6.91498850717897</v>
+        <v>6.892255208813435</v>
       </c>
       <c r="O7" t="n">
-        <v>2.629636573212916</v>
+        <v>2.625310497600891</v>
       </c>
       <c r="P7" t="n">
-        <v>373.4046218358638</v>
+        <v>373.4044457715513</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -26887,28 +26973,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1216505028167031</v>
+        <v>-0.12359637523491</v>
       </c>
       <c r="J8" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K8" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04973942771155082</v>
+        <v>0.05152047301219731</v>
       </c>
       <c r="M8" t="n">
-        <v>3.02508400670277</v>
+        <v>3.023732416798184</v>
       </c>
       <c r="N8" t="n">
-        <v>14.55478452355426</v>
+        <v>14.53359485110165</v>
       </c>
       <c r="O8" t="n">
-        <v>3.81507333134689</v>
+        <v>3.812295220874381</v>
       </c>
       <c r="P8" t="n">
-        <v>385.9993116705036</v>
+        <v>386.0204431678363</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -26950,7 +27036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54863,6 +54949,100 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-36.63917184767083,174.75078942274308</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-36.6396147011726,174.75006680037174</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-36.64003245077972,174.74931560403255</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-36.640470273916755,174.74858933775874</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-36.641014461971714,174.74798965521654</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>-36.64157333595579,174.7474163284517</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>-36.64215480231352,174.74689925664165</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-36.6391868899045,174.75080003508418</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-36.63961903241213,174.75007001496675</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-36.640034052020724,174.74931705491056</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-36.64047277703294,174.74859207151843</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>-36.64101642928331,174.7479917902576</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>-36.64157834622463,174.7474222864657</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>-36.64216055528363,174.74690712495294</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I596"/>
+  <dimension ref="A1:I597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20104,6 +20104,39 @@
         <v>380.43</v>
       </c>
       <c r="I596" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>336.65</v>
+      </c>
+      <c r="C597" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="D597" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="E597" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="F597" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="G597" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="H597" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="I597" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20120,7 +20153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26313,6 +26346,16 @@
       </c>
       <c r="B619" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26481,28 +26524,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2387861357712159</v>
+        <v>-0.2394568821889889</v>
       </c>
       <c r="J2" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K2" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02806419831520612</v>
+        <v>0.0283163565374801</v>
       </c>
       <c r="M2" t="n">
-        <v>8.413240344364191</v>
+        <v>8.402572850497236</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8972238466646</v>
+        <v>100.7336504818306</v>
       </c>
       <c r="O2" t="n">
-        <v>10.04476101491044</v>
+        <v>10.03661548938837</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8853692000234</v>
+        <v>344.8927364170101</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -26563,28 +26606,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1429880415905856</v>
+        <v>-0.1443274792924124</v>
       </c>
       <c r="J3" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K3" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1400475730807114</v>
+        <v>0.1422731446271758</v>
       </c>
       <c r="M3" t="n">
-        <v>2.092312605052551</v>
+        <v>2.093997529664096</v>
       </c>
       <c r="N3" t="n">
-        <v>6.488013378349788</v>
+        <v>6.502617502789505</v>
       </c>
       <c r="O3" t="n">
-        <v>2.547157902123421</v>
+        <v>2.550023039658564</v>
       </c>
       <c r="P3" t="n">
-        <v>351.3256315615312</v>
+        <v>351.3402328667842</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -26645,28 +26688,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1266417022312566</v>
+        <v>-0.1270960354296799</v>
       </c>
       <c r="J4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1161847262111008</v>
+        <v>0.1172501297942569</v>
       </c>
       <c r="M4" t="n">
-        <v>2.000363437281443</v>
+        <v>1.99951936861235</v>
       </c>
       <c r="N4" t="n">
-        <v>6.304917439315467</v>
+        <v>6.297271466078008</v>
       </c>
       <c r="O4" t="n">
-        <v>2.510959465884598</v>
+        <v>2.509436483770412</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4970487490464</v>
+        <v>352.5020014674205</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -26727,28 +26770,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1118485717080466</v>
+        <v>-0.1129767757589043</v>
       </c>
       <c r="J5" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K5" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1144746302792888</v>
+        <v>0.1165274991608165</v>
       </c>
       <c r="M5" t="n">
-        <v>1.731080743029618</v>
+        <v>1.732905630653302</v>
       </c>
       <c r="N5" t="n">
-        <v>5.001106523466578</v>
+        <v>5.010799676224853</v>
       </c>
       <c r="O5" t="n">
-        <v>2.236315389981158</v>
+        <v>2.238481555926886</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0642897547812</v>
+        <v>351.0765883870444</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -26809,28 +26852,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02919530724700642</v>
+        <v>-0.02941406065294437</v>
       </c>
       <c r="J6" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K6" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009527991472864206</v>
+        <v>0.009703393332553989</v>
       </c>
       <c r="M6" t="n">
-        <v>1.680706257534211</v>
+        <v>1.678926323436494</v>
       </c>
       <c r="N6" t="n">
-        <v>4.579102957731908</v>
+        <v>4.572099783900555</v>
       </c>
       <c r="O6" t="n">
-        <v>2.139883865477729</v>
+        <v>2.138246894982091</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3063704939107</v>
+        <v>355.308755140282</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -26891,28 +26934,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1489005613711218</v>
+        <v>-0.1484097670408148</v>
       </c>
       <c r="J7" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K7" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L7" t="n">
-        <v>0.142546162410966</v>
+        <v>0.1421234741272813</v>
       </c>
       <c r="M7" t="n">
-        <v>2.070482279671596</v>
+        <v>2.069134853463745</v>
       </c>
       <c r="N7" t="n">
-        <v>6.892255208813435</v>
+        <v>6.884113374986926</v>
       </c>
       <c r="O7" t="n">
-        <v>2.625310497600891</v>
+        <v>2.623759397312742</v>
       </c>
       <c r="P7" t="n">
-        <v>373.4044457715513</v>
+        <v>373.3990955877962</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -26973,28 +27016,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.12359637523491</v>
+        <v>-0.1242437593471091</v>
       </c>
       <c r="J8" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K8" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05152047301219731</v>
+        <v>0.05219287975399922</v>
       </c>
       <c r="M8" t="n">
-        <v>3.023732416798184</v>
+        <v>3.021574561396229</v>
       </c>
       <c r="N8" t="n">
-        <v>14.53359485110165</v>
+        <v>14.51516418617487</v>
       </c>
       <c r="O8" t="n">
-        <v>3.812295220874381</v>
+        <v>3.809877187807354</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0204431678363</v>
+        <v>386.0275003478942</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -27036,7 +27079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I596"/>
+  <dimension ref="A1:I597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55043,6 +55086,53 @@
         </is>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-36.63922112665102,174.75082418923043</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-36.63962506520989,174.750074492439</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-36.640038055123156,174.74932068210595</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-36.64047832447939,174.74859813012165</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-36.64102029606806,174.74799598671797</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>-36.64158491813521,174.7474301015242</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-36.64216321981697,174.7469107692239</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I597"/>
+  <dimension ref="A1:I599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20139,6 +20139,72 @@
       <c r="I597" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="C598" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="D598" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="E598" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="F598" t="n">
+        <v>354.51</v>
+      </c>
+      <c r="G598" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="H598" t="n">
+        <v>382.88</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="C599" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="D599" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="E599" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="F599" t="n">
+        <v>354.51</v>
+      </c>
+      <c r="G599" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="H599" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26356,6 +26422,26 @@
       </c>
       <c r="B620" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -26524,34 +26610,30 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2394568821889889</v>
+        <v>-0.2348061620755914</v>
       </c>
       <c r="J2" t="n">
+        <v>598</v>
+      </c>
+      <c r="K2" t="n">
         <v>596</v>
       </c>
-      <c r="K2" t="n">
-        <v>594</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0283163565374801</v>
+        <v>0.02741307557562889</v>
       </c>
       <c r="M2" t="n">
-        <v>8.402572850497236</v>
+        <v>8.395109436615106</v>
       </c>
       <c r="N2" t="n">
-        <v>100.7336504818306</v>
+        <v>100.5458572926917</v>
       </c>
       <c r="O2" t="n">
-        <v>10.03661548938837</v>
+        <v>10.02725572091845</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8927364170101</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>344.8414448997431</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.74896349948156 -36.636583627078274, 174.75404994831172 -36.643793077085235)</t>
@@ -26606,34 +26688,30 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1443274792924124</v>
+        <v>-0.1462574813951242</v>
       </c>
       <c r="J3" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K3" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1422731446271758</v>
+        <v>0.1459549753432631</v>
       </c>
       <c r="M3" t="n">
-        <v>2.093997529664096</v>
+        <v>2.094460321467338</v>
       </c>
       <c r="N3" t="n">
-        <v>6.502617502789505</v>
+        <v>6.507175328060414</v>
       </c>
       <c r="O3" t="n">
-        <v>2.550023039658564</v>
+        <v>2.550916566267978</v>
       </c>
       <c r="P3" t="n">
-        <v>351.3402328667842</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>351.3613591809946</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.74810189034943 -36.636967135064864, 174.7533845612848 -36.644084627395394)</t>
@@ -26688,34 +26766,30 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1270960354296799</v>
+        <v>-0.12758030870058</v>
       </c>
       <c r="J4" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K4" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1172501297942569</v>
+        <v>0.1187777596747167</v>
       </c>
       <c r="M4" t="n">
-        <v>1.99951936861235</v>
+        <v>1.995487959902724</v>
       </c>
       <c r="N4" t="n">
-        <v>6.297271466078008</v>
+        <v>6.277866578500969</v>
       </c>
       <c r="O4" t="n">
-        <v>2.509436483770412</v>
+        <v>2.50556711714154</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5020014674205</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>352.5073024474858</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.74702685357488 -36.63750639578563, 174.75309668486483 -36.64420509276497)</t>
@@ -26770,34 +26844,30 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1129767757589043</v>
+        <v>-0.1144809788135879</v>
       </c>
       <c r="J5" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K5" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1165274991608165</v>
+        <v>0.1197141261222516</v>
       </c>
       <c r="M5" t="n">
-        <v>1.732905630653302</v>
+        <v>1.733414081596547</v>
       </c>
       <c r="N5" t="n">
-        <v>5.010799676224853</v>
+        <v>5.010020067980693</v>
       </c>
       <c r="O5" t="n">
-        <v>2.238481555926886</v>
+        <v>2.238307411411733</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0765883870444</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>351.0930537920764</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.74605049059147 -36.63814552593046, 174.75285165979534 -36.64437270888496)</t>
@@ -26852,34 +26922,30 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02941406065294437</v>
+        <v>-0.02942895841516932</v>
       </c>
       <c r="J6" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K6" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009703393332553989</v>
+        <v>0.009783928997438296</v>
       </c>
       <c r="M6" t="n">
-        <v>1.678926323436494</v>
+        <v>1.673381180343086</v>
       </c>
       <c r="N6" t="n">
-        <v>4.572099783900555</v>
+        <v>4.556810048056372</v>
       </c>
       <c r="O6" t="n">
-        <v>2.138246894982091</v>
+        <v>2.134668603801623</v>
       </c>
       <c r="P6" t="n">
-        <v>355.308755140282</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>355.3089182140664</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.7453905813196 -36.63861946653374, 174.75216745703452 -36.6448637820305)</t>
@@ -26934,34 +27000,30 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1484097670408148</v>
+        <v>-0.1471838869745967</v>
       </c>
       <c r="J7" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K7" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1421234741272813</v>
+        <v>0.1407838209734564</v>
       </c>
       <c r="M7" t="n">
-        <v>2.069134853463745</v>
+        <v>2.067471440373764</v>
       </c>
       <c r="N7" t="n">
-        <v>6.884113374986926</v>
+        <v>6.873290480757229</v>
       </c>
       <c r="O7" t="n">
-        <v>2.623759397312742</v>
+        <v>2.621696107629034</v>
       </c>
       <c r="P7" t="n">
-        <v>373.3990955877962</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>373.3856791422079</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.74456020746882 -36.63917142797457, 174.7516831472094 -36.64516117991589)</t>
@@ -27016,34 +27078,30 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1242437593471091</v>
+        <v>-0.1245070889883196</v>
       </c>
       <c r="J8" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K8" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05219287975399922</v>
+        <v>0.05276325839878848</v>
       </c>
       <c r="M8" t="n">
-        <v>3.021574561396229</v>
+        <v>3.013128325755126</v>
       </c>
       <c r="N8" t="n">
-        <v>14.51516418617487</v>
+        <v>14.46803499899499</v>
       </c>
       <c r="O8" t="n">
-        <v>3.809877187807354</v>
+        <v>3.803687026950954</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0275003478942</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>386.0303846381116</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.74375633232293 -36.63985671876029, 174.7513815083659 -36.645431803238544)</t>
@@ -27079,7 +27137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I597"/>
+  <dimension ref="A1:I599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55133,6 +55191,100 @@
         </is>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-36.639288738332894,174.75087188958787</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-36.63963318628349,174.75008051980657</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-36.640042422143864,174.7493246390468</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-36.64048556321997,174.7486060358613</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-36.64102443420596,174.7480004776672</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-36.64159168525047,174.74743814871456</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-36.6421753918882,174.74692741691916</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-36.639288738332894,174.75087188958787</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-36.63963318628349,174.75008051980657</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-36.640042422143864,174.7493246390468</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-36.64048556321997,174.7486060358613</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-36.64102443420596,174.7480004776672</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>-36.64158270580892,174.74742747071227</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-36.64216903334383,174.74691872036126</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I599"/>
+  <dimension ref="A1:I602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20203,6 +20203,105 @@
         <v>381.83</v>
       </c>
       <c r="I599" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="C600" t="n">
+        <v>344.47</v>
+      </c>
+      <c r="D600" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="E600" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="F600" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="G600" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="H600" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="C601" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="D601" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="E601" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="F601" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="G601" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="H601" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>344.52</v>
+      </c>
+      <c r="C602" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="D602" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="E602" t="n">
+        <v>346.43</v>
+      </c>
+      <c r="F602" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="G602" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="H602" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="I602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20219,7 +20318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26442,6 +26541,36 @@
       </c>
       <c r="B622" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -26610,28 +26739,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2348061620755914</v>
+        <v>-0.2286760296839904</v>
       </c>
       <c r="J2" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02741307557562889</v>
+        <v>0.0262720274170537</v>
       </c>
       <c r="M2" t="n">
-        <v>8.395109436615106</v>
+        <v>8.380355633027852</v>
       </c>
       <c r="N2" t="n">
-        <v>100.5458572926917</v>
+        <v>100.2212455227391</v>
       </c>
       <c r="O2" t="n">
-        <v>10.02725572091845</v>
+        <v>10.01105616419862</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8414448997431</v>
+        <v>344.7736530464279</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26688,28 +26817,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1462574813951242</v>
+        <v>-0.1498432624176643</v>
       </c>
       <c r="J3" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1459549753432631</v>
+        <v>0.1522846419450026</v>
       </c>
       <c r="M3" t="n">
-        <v>2.094460321467338</v>
+        <v>2.09779605498219</v>
       </c>
       <c r="N3" t="n">
-        <v>6.507175328060414</v>
+        <v>6.536500046298221</v>
       </c>
       <c r="O3" t="n">
-        <v>2.550916566267978</v>
+        <v>2.556657983833235</v>
       </c>
       <c r="P3" t="n">
-        <v>351.3613591809946</v>
+        <v>351.4007255939063</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26766,28 +26895,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.12758030870058</v>
+        <v>-0.1287786077086106</v>
       </c>
       <c r="J4" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1187777596747167</v>
+        <v>0.1217951734018483</v>
       </c>
       <c r="M4" t="n">
-        <v>1.995487959902724</v>
+        <v>1.992068638397941</v>
       </c>
       <c r="N4" t="n">
-        <v>6.277866578500969</v>
+        <v>6.253599671416356</v>
       </c>
       <c r="O4" t="n">
-        <v>2.50556711714154</v>
+        <v>2.500719830652038</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5073024474858</v>
+        <v>352.5204584614351</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26844,28 +26973,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1144809788135879</v>
+        <v>-0.1157925740320293</v>
       </c>
       <c r="J5" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K5" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1197141261222516</v>
+        <v>0.1231182625557062</v>
       </c>
       <c r="M5" t="n">
-        <v>1.733414081596547</v>
+        <v>1.73032203014323</v>
       </c>
       <c r="N5" t="n">
-        <v>5.010020067980693</v>
+        <v>4.994095551621451</v>
       </c>
       <c r="O5" t="n">
-        <v>2.238307411411733</v>
+        <v>2.234747312700354</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0930537920764</v>
+        <v>351.1074513949863</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26922,28 +27051,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02942895841516932</v>
+        <v>-0.02892497622125003</v>
       </c>
       <c r="J6" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K6" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009783928997438296</v>
+        <v>0.0095543376463052</v>
       </c>
       <c r="M6" t="n">
-        <v>1.673381180343086</v>
+        <v>1.667556206678168</v>
       </c>
       <c r="N6" t="n">
-        <v>4.556810048056372</v>
+        <v>4.535790366397055</v>
       </c>
       <c r="O6" t="n">
-        <v>2.134668603801623</v>
+        <v>2.1297395066996</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3089182140664</v>
+        <v>355.3033867746383</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27000,28 +27129,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1471838869745967</v>
+        <v>-0.1451189914998021</v>
       </c>
       <c r="J7" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K7" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1407838209734564</v>
+        <v>0.1383402966134791</v>
       </c>
       <c r="M7" t="n">
-        <v>2.067471440373764</v>
+        <v>2.065993829154735</v>
       </c>
       <c r="N7" t="n">
-        <v>6.873290480757229</v>
+        <v>6.859816011074317</v>
       </c>
       <c r="O7" t="n">
-        <v>2.621696107629034</v>
+        <v>2.619125046857121</v>
       </c>
       <c r="P7" t="n">
-        <v>373.3856791422079</v>
+        <v>373.3630124218327</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27078,28 +27207,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1245070889883196</v>
+        <v>-0.1246299952356446</v>
       </c>
       <c r="J8" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K8" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05276325839878848</v>
+        <v>0.05341155955373567</v>
       </c>
       <c r="M8" t="n">
-        <v>3.013128325755126</v>
+        <v>2.999372645083632</v>
       </c>
       <c r="N8" t="n">
-        <v>14.46803499899499</v>
+        <v>14.39620353714789</v>
       </c>
       <c r="O8" t="n">
-        <v>3.803687026950954</v>
+        <v>3.794232931324576</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0303846381116</v>
+        <v>386.0317320079114</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27137,7 +27266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I599"/>
+  <dimension ref="A1:I602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55285,6 +55414,147 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-36.63929132371544,174.75087371358933</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-36.63963140738169,174.75007919952597</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-36.64004089368663,174.74932325411746</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-36.64048968997837,174.7486105428724</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-36.641027554768826,174.748003864285</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>-36.64158817155607,174.74743397036556</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-36.64217327237348,174.74692451806635</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-36.639275654729914,174.75086265903698</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-36.63962398240005,174.75007368879008</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-36.6400368178006,174.7493195609728</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-36.640495575682635,174.7486169709055</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-36.641030743169914,174.74800732452522</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-36.64159181538728,174.74743830346824</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-36.64217212177975,174.74692294440348</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-36.63928278411847,174.75086768885774</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-36.63962684411175,174.75007581271942</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-36.640038928527304,174.7493214734941</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-36.64048921641593,174.74861002567437</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-36.6410254517808,174.74800158199906</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-36.64158647977724,174.747431958568</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-36.64217575523356,174.74692791386533</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:I604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20302,6 +20302,72 @@
         <v>382.94</v>
       </c>
       <c r="I602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>342.89</v>
+      </c>
+      <c r="C603" t="n">
+        <v>343.67</v>
+      </c>
+      <c r="D603" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="E603" t="n">
+        <v>346.77</v>
+      </c>
+      <c r="F603" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="G603" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="H603" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>344.04</v>
+      </c>
+      <c r="C604" t="n">
+        <v>343.98</v>
+      </c>
+      <c r="D604" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="E604" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="F604" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="G604" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="H604" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="I604" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20318,7 +20384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26571,6 +26637,26 @@
       </c>
       <c r="B625" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -26739,28 +26825,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2286760296839904</v>
+        <v>-0.2254164368991395</v>
       </c>
       <c r="J2" t="n">
+        <v>603</v>
+      </c>
+      <c r="K2" t="n">
         <v>601</v>
       </c>
-      <c r="K2" t="n">
-        <v>599</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0262720274170537</v>
+        <v>0.02571082736024999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.380355633027852</v>
+        <v>8.366982821073623</v>
       </c>
       <c r="N2" t="n">
-        <v>100.2212455227391</v>
+        <v>99.96400143063046</v>
       </c>
       <c r="O2" t="n">
-        <v>10.01105616419862</v>
+        <v>9.998199909515236</v>
       </c>
       <c r="P2" t="n">
-        <v>344.7736530464279</v>
+        <v>344.7374923650985</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26817,28 +26903,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1498432624176643</v>
+        <v>-0.1522673735631949</v>
       </c>
       <c r="J3" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K3" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1522846419450026</v>
+        <v>0.1565783700128971</v>
       </c>
       <c r="M3" t="n">
-        <v>2.09779605498219</v>
+        <v>2.100074495381041</v>
       </c>
       <c r="N3" t="n">
-        <v>6.536500046298221</v>
+        <v>6.557195962763643</v>
       </c>
       <c r="O3" t="n">
-        <v>2.556657983833235</v>
+        <v>2.560702240160625</v>
       </c>
       <c r="P3" t="n">
-        <v>351.4007255939063</v>
+        <v>351.4274141413548</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26895,28 +26981,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1287786077086106</v>
+        <v>-0.1295263007452421</v>
       </c>
       <c r="J4" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K4" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1217951734018483</v>
+        <v>0.1237452521746979</v>
       </c>
       <c r="M4" t="n">
-        <v>1.992068638397941</v>
+        <v>1.989532224177024</v>
       </c>
       <c r="N4" t="n">
-        <v>6.253599671416356</v>
+        <v>6.23748115159664</v>
       </c>
       <c r="O4" t="n">
-        <v>2.500719830652038</v>
+        <v>2.497494975289568</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5204584614351</v>
+        <v>352.5286877383732</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26973,28 +27059,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1157925740320293</v>
+        <v>-0.1163579784120997</v>
       </c>
       <c r="J5" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K5" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1231182625557062</v>
+        <v>0.1249031832293978</v>
       </c>
       <c r="M5" t="n">
-        <v>1.73032203014323</v>
+        <v>1.726960993667849</v>
       </c>
       <c r="N5" t="n">
-        <v>4.994095551621451</v>
+        <v>4.980425114086868</v>
       </c>
       <c r="O5" t="n">
-        <v>2.234747312700354</v>
+        <v>2.23168660749821</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1074513949863</v>
+        <v>351.1136736742423</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27051,28 +27137,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02892497622125003</v>
+        <v>-0.02817410544281759</v>
       </c>
       <c r="J6" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K6" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0095543376463052</v>
+        <v>0.009125387723037726</v>
       </c>
       <c r="M6" t="n">
-        <v>1.667556206678168</v>
+        <v>1.665747407059622</v>
       </c>
       <c r="N6" t="n">
-        <v>4.535790366397055</v>
+        <v>4.525422472035367</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1297395066996</v>
+        <v>2.127304038456978</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3033867746383</v>
+        <v>355.2951166827447</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27129,28 +27215,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1451189914998021</v>
+        <v>-0.1427628217615049</v>
       </c>
       <c r="J7" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K7" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1383402966134791</v>
+        <v>0.1346450785205426</v>
       </c>
       <c r="M7" t="n">
-        <v>2.065993829154735</v>
+        <v>2.069231686852524</v>
       </c>
       <c r="N7" t="n">
-        <v>6.859816011074317</v>
+        <v>6.877419462730481</v>
       </c>
       <c r="O7" t="n">
-        <v>2.619125046857121</v>
+        <v>2.622483453280589</v>
       </c>
       <c r="P7" t="n">
-        <v>373.3630124218327</v>
+        <v>373.3370683906149</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27207,28 +27293,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1246299952356446</v>
+        <v>-0.1242064833055343</v>
       </c>
       <c r="J8" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K8" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05341155955373567</v>
+        <v>0.05343018997091575</v>
       </c>
       <c r="M8" t="n">
-        <v>2.999372645083632</v>
+        <v>2.991655459232156</v>
       </c>
       <c r="N8" t="n">
-        <v>14.39620353714789</v>
+        <v>14.34980318325177</v>
       </c>
       <c r="O8" t="n">
-        <v>3.794232931324576</v>
+        <v>3.788113406862547</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0317320079114</v>
+        <v>386.0270682071967</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27266,7 +27352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:I604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55555,6 +55641,100 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-36.63927001389482,174.75085867939924</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-36.639625219897006,174.75007460724598</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-36.6400360899638,174.74931890148272</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-36.64049151657628,174.7486125377791</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>-36.64102918288854,174.74800563121613</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-36.64159610990243,174.74744341033977</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-36.6421773902877,174.74693015012335</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-36.63927902356189,174.75086503576534</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-36.63962761754735,174.7500763867544</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-36.6400422765765,174.74932450714874</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-36.64049719932512,174.74861874415615</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>-36.641035084822285,174.74801203634215</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-36.641600729759354,174.7474489040962</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-36.64217896478426,174.74693230355706</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I604"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20368,6 +20368,204 @@
         <v>383.47</v>
       </c>
       <c r="I604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="C605" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="D605" t="n">
+        <v>348.95</v>
+      </c>
+      <c r="E605" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="F605" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="G605" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="H605" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>340.76</v>
+      </c>
+      <c r="C606" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="D606" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="E606" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="F606" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="G606" t="n">
+        <v>372.61</v>
+      </c>
+      <c r="H606" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="C607" t="n">
+        <v>344.07</v>
+      </c>
+      <c r="D607" t="n">
+        <v>348.52</v>
+      </c>
+      <c r="E607" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="F607" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="G607" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="H607" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="C608" t="n">
+        <v>344.04</v>
+      </c>
+      <c r="D608" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="E608" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="F608" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="G608" t="n">
+        <v>372</v>
+      </c>
+      <c r="H608" t="n">
+        <v>381.19</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>332.87</v>
+      </c>
+      <c r="C609" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="D609" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="E609" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="F609" t="n">
+        <v>356.69</v>
+      </c>
+      <c r="G609" t="n">
+        <v>371.49</v>
+      </c>
+      <c r="H609" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="C610" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="D610" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="E610" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="F610" t="n">
+        <v>357.53</v>
+      </c>
+      <c r="G610" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="H610" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="I610" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20384,7 +20582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26657,6 +26855,66 @@
       </c>
       <c r="B627" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -26825,28 +27083,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2254164368991395</v>
+        <v>-0.2296070736659968</v>
       </c>
       <c r="J2" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K2" t="n">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02571082736024999</v>
+        <v>0.02715505708651367</v>
       </c>
       <c r="M2" t="n">
-        <v>8.366982821073623</v>
+        <v>8.326897343970467</v>
       </c>
       <c r="N2" t="n">
-        <v>99.96400143063046</v>
+        <v>99.21388137729993</v>
       </c>
       <c r="O2" t="n">
-        <v>9.998199909515236</v>
+        <v>9.960616515924098</v>
       </c>
       <c r="P2" t="n">
-        <v>344.7374923650985</v>
+        <v>344.7842765161536</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26903,28 +27161,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1522673735631949</v>
+        <v>-0.1585503956306178</v>
       </c>
       <c r="J3" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K3" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1565783700128971</v>
+        <v>0.1685123610200842</v>
       </c>
       <c r="M3" t="n">
-        <v>2.100074495381041</v>
+        <v>2.103439584376618</v>
       </c>
       <c r="N3" t="n">
-        <v>6.557195962763643</v>
+        <v>6.589074535150844</v>
       </c>
       <c r="O3" t="n">
-        <v>2.560702240160625</v>
+        <v>2.566919269309194</v>
       </c>
       <c r="P3" t="n">
-        <v>351.4274141413548</v>
+        <v>351.4968587270959</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26981,28 +27239,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1295263007452421</v>
+        <v>-0.1303014497801401</v>
       </c>
       <c r="J4" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K4" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1237452521746979</v>
+        <v>0.1273950287425568</v>
       </c>
       <c r="M4" t="n">
-        <v>1.989532224177024</v>
+        <v>1.974070390836499</v>
       </c>
       <c r="N4" t="n">
-        <v>6.23748115159664</v>
+        <v>6.177737118400898</v>
       </c>
       <c r="O4" t="n">
-        <v>2.497494975289568</v>
+        <v>2.485505405023473</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5286877383732</v>
+        <v>352.5372571082427</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27059,28 +27317,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1163579784120997</v>
+        <v>-0.1145471215095391</v>
       </c>
       <c r="J5" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K5" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1249031832293978</v>
+        <v>0.1235420266016835</v>
       </c>
       <c r="M5" t="n">
-        <v>1.726960993667849</v>
+        <v>1.720803678755339</v>
       </c>
       <c r="N5" t="n">
-        <v>4.980425114086868</v>
+        <v>4.944819709663234</v>
       </c>
       <c r="O5" t="n">
-        <v>2.23168660749821</v>
+        <v>2.223695057705358</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1136736742423</v>
+        <v>351.0936392994475</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27137,28 +27395,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02817410544281759</v>
+        <v>-0.02379666930912549</v>
       </c>
       <c r="J6" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K6" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009125387723037726</v>
+        <v>0.006597729787800377</v>
       </c>
       <c r="M6" t="n">
-        <v>1.665747407059622</v>
+        <v>1.671215439024499</v>
       </c>
       <c r="N6" t="n">
-        <v>4.525422472035367</v>
+        <v>4.529275108360268</v>
       </c>
       <c r="O6" t="n">
-        <v>2.127304038456978</v>
+        <v>2.128209366664913</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2951166827447</v>
+        <v>355.2467251357876</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27215,28 +27473,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1427628217615049</v>
+        <v>-0.1372681963510304</v>
       </c>
       <c r="J7" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K7" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1346450785205426</v>
+        <v>0.1269135479983441</v>
       </c>
       <c r="M7" t="n">
-        <v>2.069231686852524</v>
+        <v>2.072459977347608</v>
       </c>
       <c r="N7" t="n">
-        <v>6.877419462730481</v>
+        <v>6.885806980931462</v>
       </c>
       <c r="O7" t="n">
-        <v>2.622483453280589</v>
+        <v>2.624082121605851</v>
       </c>
       <c r="P7" t="n">
-        <v>373.3370683906149</v>
+        <v>373.2763452298977</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27293,28 +27551,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1242064833055343</v>
+        <v>-0.1264156489955225</v>
       </c>
       <c r="J8" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K8" t="n">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05343018997091575</v>
+        <v>0.0563076015802968</v>
       </c>
       <c r="M8" t="n">
-        <v>2.991655459232156</v>
+        <v>2.97292601561919</v>
       </c>
       <c r="N8" t="n">
-        <v>14.34980318325177</v>
+        <v>14.2275732862924</v>
       </c>
       <c r="O8" t="n">
-        <v>3.788113406862547</v>
+        <v>3.771945557175023</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0270682071967</v>
+        <v>386.051505531731</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27352,7 +27610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I604"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55735,6 +55993,288 @@
         </is>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-36.63927017058469,174.75085878994474</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-36.63963187144303,174.75007954394698</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-36.64004620689502,174.74932806839587</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-36.64049875531581,174.74862044352147</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-36.64103589888207,174.74801291980785</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-36.64159767154424,174.7474452673841</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-36.64217575523356,174.74692791386533</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-36.63925332642347,174.7508469063078</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-36.63962970582341,174.7500779366489</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-36.6400441689521,174.74932622182325</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-36.6404996347888,174.74862140403232</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-36.6410368486185,174.7480139505179</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-36.641595979765604,174.7474432555861</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-36.6421729090281,174.74692402112018</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-36.639234366947356,174.75083353031343</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-36.63962831363937,174.7500769033859</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-36.640043077196964,174.74932523258795</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-36.64050748239355,174.7486299747455</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-36.64104024053421,174.7480176316254</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-36.64159181538728,174.74743830346824</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-36.64216685327132,174.7469157386846</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-36.63920694621437,174.7508141848789</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-36.63962808160869,174.7500767311754</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-36.64004511513989,174.74932707916057</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-36.64050870012527,174.74863130468393</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-36.641040715402404,174.74801814698048</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-36.64159201059252,174.74743853559875</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-36.64216515765932,174.74691341960286</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-36.63919151225733,174.750803296169</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-36.639627230829554,174.7500760997369</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-36.640042713278575,174.74932490284286</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-36.64050971490168,174.74863241296597</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-36.64103922295951,174.74801652729312</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-36.6415886921034,174.7474345893802</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-36.64216001026543,174.74690637953393</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-36.63916965401167,174.75078787511035</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-36.639630247228325,174.7500783384734</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-36.6400441689521,174.74932622182325</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-36.640512015061525,174.74863492507203</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-36.64104492137768,174.74802271155428</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-36.64159767154424,174.7474452673841</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-36.64216503654417,174.74691325395418</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I610"/>
+  <dimension ref="A1:I613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20566,6 +20566,105 @@
         <v>381.17</v>
       </c>
       <c r="I610" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>325.26</v>
+      </c>
+      <c r="C611" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="D611" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="E611" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="F611" t="n">
+        <v>357.39</v>
+      </c>
+      <c r="G611" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="H611" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>320.59</v>
+      </c>
+      <c r="C612" t="n">
+        <v>343.66</v>
+      </c>
+      <c r="D612" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="E612" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="F612" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="G612" t="n">
+        <v>373.34</v>
+      </c>
+      <c r="H612" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="C613" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="D613" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="E613" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="F613" t="n">
+        <v>357.59</v>
+      </c>
+      <c r="G613" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="H613" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="I613" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20582,7 +20681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26914,6 +27013,36 @@
         </is>
       </c>
       <c r="B633" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
         <v>-0.89</v>
       </c>
     </row>
@@ -27083,28 +27212,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2296070736659968</v>
+        <v>-0.2472426649577125</v>
       </c>
       <c r="J2" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K2" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02715505708651367</v>
+        <v>0.0311934619491826</v>
       </c>
       <c r="M2" t="n">
-        <v>8.326897343970467</v>
+        <v>8.379575151464298</v>
       </c>
       <c r="N2" t="n">
-        <v>99.21388137729993</v>
+        <v>100.3092317960676</v>
       </c>
       <c r="O2" t="n">
-        <v>9.960616515924098</v>
+        <v>10.01544965521107</v>
       </c>
       <c r="P2" t="n">
-        <v>344.7842765161536</v>
+        <v>344.9814743379363</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27161,28 +27290,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1585503956306178</v>
+        <v>-0.1622080289336102</v>
       </c>
       <c r="J3" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K3" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1685123610200842</v>
+        <v>0.1750766666259372</v>
       </c>
       <c r="M3" t="n">
-        <v>2.103439584376618</v>
+        <v>2.107590866464538</v>
       </c>
       <c r="N3" t="n">
-        <v>6.589074535150844</v>
+        <v>6.623547654527593</v>
       </c>
       <c r="O3" t="n">
-        <v>2.566919269309194</v>
+        <v>2.573625391257942</v>
       </c>
       <c r="P3" t="n">
-        <v>351.4968587270959</v>
+        <v>351.5374522134616</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27239,28 +27368,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1303014497801401</v>
+        <v>-0.1309817762484876</v>
       </c>
       <c r="J4" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K4" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1273950287425568</v>
+        <v>0.1297110008511323</v>
       </c>
       <c r="M4" t="n">
-        <v>1.974070390836499</v>
+        <v>1.96797707104599</v>
       </c>
       <c r="N4" t="n">
-        <v>6.177737118400898</v>
+        <v>6.149914631324685</v>
       </c>
       <c r="O4" t="n">
-        <v>2.485505405023473</v>
+        <v>2.479902141481531</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5372571082427</v>
+        <v>352.5448090849247</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27317,28 +27446,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1145471215095391</v>
+        <v>-0.1126812676948684</v>
       </c>
       <c r="J5" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K5" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1235420266016835</v>
+        <v>0.1207842466316683</v>
       </c>
       <c r="M5" t="n">
-        <v>1.720803678755339</v>
+        <v>1.722919423881625</v>
       </c>
       <c r="N5" t="n">
-        <v>4.944819709663234</v>
+        <v>4.937979324599879</v>
       </c>
       <c r="O5" t="n">
-        <v>2.223695057705358</v>
+        <v>2.222156458172979</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0936392994475</v>
+        <v>351.072932312671</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27395,28 +27524,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02379666930912549</v>
+        <v>-0.02082234797890162</v>
       </c>
       <c r="J6" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K6" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006597729787800377</v>
+        <v>0.005063715396594892</v>
       </c>
       <c r="M6" t="n">
-        <v>1.671215439024499</v>
+        <v>1.677844387774476</v>
       </c>
       <c r="N6" t="n">
-        <v>4.529275108360268</v>
+        <v>4.551410779506344</v>
       </c>
       <c r="O6" t="n">
-        <v>2.128209366664913</v>
+        <v>2.13340356695735</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2467251357876</v>
+        <v>355.2137163458692</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27473,28 +27602,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1372681963510304</v>
+        <v>-0.1338132210097054</v>
       </c>
       <c r="J7" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K7" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1269135479983441</v>
+        <v>0.1215717268497452</v>
       </c>
       <c r="M7" t="n">
-        <v>2.072459977347608</v>
+        <v>2.077280375022734</v>
       </c>
       <c r="N7" t="n">
-        <v>6.885806980931462</v>
+        <v>6.912456667858034</v>
       </c>
       <c r="O7" t="n">
-        <v>2.624082121605851</v>
+        <v>2.629155124342806</v>
       </c>
       <c r="P7" t="n">
-        <v>373.2763452298977</v>
+        <v>373.2379992686229</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27551,28 +27680,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1264156489955225</v>
+        <v>-0.1292497537796593</v>
       </c>
       <c r="J8" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K8" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0563076015802968</v>
+        <v>0.05914279313749515</v>
       </c>
       <c r="M8" t="n">
-        <v>2.97292601561919</v>
+        <v>2.971254599925389</v>
       </c>
       <c r="N8" t="n">
-        <v>14.2275732862924</v>
+        <v>14.19848432052569</v>
       </c>
       <c r="O8" t="n">
-        <v>3.771945557175023</v>
+        <v>3.768087621131665</v>
       </c>
       <c r="P8" t="n">
-        <v>386.051505531731</v>
+        <v>386.0829612882076</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27610,7 +27739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I610"/>
+  <dimension ref="A1:I613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56275,6 +56404,147 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-36.63913189173234,174.75076123373245</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-36.63962444646141,174.75007403321104</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-36.64004278606225,174.74932496879188</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-36.640512218016795,174.74863514672847</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-36.64104397164135,174.74802168084403</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-36.64159532908151,174.74744248181764</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-36.64215667959856,174.74690182419573</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.63909530462113,174.7507354214684</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.639625142553456,174.7500745498425</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.64004278606225,174.74932496879188</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.64051370635548,174.74863677220895</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.641047499233416,174.74802550919654</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-36.641600729759354,174.7474489040962</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-36.64215928357449,174.74690538564195</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.63906561186444,174.75071447320386</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.639622744903086,174.7500727703342</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.64004002028249,174.74932246272928</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.64051255627559,174.74863551615582</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.641045328407536,174.74802315328725</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-36.64160164071702,174.74744998737216</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-36.64215395450736,174.74689809710114</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
